--- a/templates/questions_template.xlsx
+++ b/templates/questions_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="how_to" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,20 +427,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,15 +489,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>time_s</t>
         </is>
@@ -503,7 +521,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>S1-Q01</t>
+          <t>Q01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -513,40 +531,211 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Exemple : combien de bits dans un octet ?</t>
+          <t>One correct answer: which component measures the temperature?</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>The sensor</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>The gateway</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>The broker</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>The dashboard</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>20</v>
+      <c r="N2" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Several correct answers: which are organs of an IoT object?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>A sensor</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>A microcontroller</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>A touch screen</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>A radio</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>A power source</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>A,B,D,E</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Up to 8 options: default MQTT port?</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SV01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sondage</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Survey (empty 'correct'): the pace of the course was</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Too slow</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Too fast</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -569,49 +758,35 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>One question per row in the sheet 'questions'. Do not rename the column headers.</t>
+          <t>One question per row. Options in columns A to H (2 to 8 options). Leave unused option columns empty.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ref: your identifier (e.g. S1-Q03). Importing a row with an existing ref in the same module replaces the question.</t>
+          <t>correct: letters of the correct options, e.g. C or A,D. EMPTY = survey question (opinion, not graded).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chapter: free text used to filter (e.g. S1).</t>
+          <t>points: weight of the question (default 1). time_s: time in seconds (default 30).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A to E: the options (2 to 5). Leave the unused columns empty.</t>
+          <t>ref: your identifier. Importing again a row with the same ref (same module) replaces the question, never duplicates it.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>correct: letter(s) of the correct option(s): C  or  A,D  (several letters = several correct answers, partial marks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>points: weight of the question (default 1). time_s: time allowed in seconds (default 30).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Questions and options may be written in French.</t>
+          <t>chapter: e.g. S1, S2... It is used to filter and for the random draw.</t>
         </is>
       </c>
     </row>

--- a/templates/questions_template.xlsx
+++ b/templates/questions_template.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,26 @@
           <t>time_s</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tolerance</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -737,6 +757,127 @@
       <c r="N5" s="2" t="n">
         <v>30</v>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Numeric (value): divider output for 4.5 V at the input?</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Numeric (range): mean temperature measured in the room?</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10..40</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Numeric (one value per board): sqrt(N) for your filter window?</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1:2; 2:2.236; 3:2.449</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -749,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -790,6 +931,20 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUMERIC questions (self-paced quizzes only): type = number; leave A..H and correct empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>answer = a value (3), a range (10..40) or one value per board / variant (1:2; 2:2.24). tolerance = accepted error in % (default 5). unit = shown next to the box.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
